--- a/25190/25190-tests.xlsx
+++ b/25190/25190-tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ize3e65\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\servicenow\DIGITALL\25190\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F7771D5-62D2-48FC-B4AA-6AA26B186338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B896FF-23EF-40CC-BE8B-49D605213217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="705" yWindow="705" windowWidth="20145" windowHeight="9990" xr2:uid="{881B2253-DBAB-4A19-9FF1-9031768B5A3A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{881B2253-DBAB-4A19-9FF1-9031768B5A3A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
   <si>
     <t>Testschritt</t>
   </si>
@@ -51,12 +48,6 @@
     <t>Ist-Ergebnis</t>
   </si>
   <si>
-    <t>Status (Pass/Fail)</t>
-  </si>
-  <si>
-    <t>Bemerkung</t>
-  </si>
-  <si>
     <t>TC-01 – Anmeldung (Vorbedingung)</t>
   </si>
   <si>
@@ -169,12 +160,6 @@
   </si>
   <si>
     <t>Letzte Änderung wird mit Datum und Uhrzeit angezeigt (Format lt. Vorgabe, z. B. TT.MM.JJJJ HH:MM)</t>
-  </si>
-  <si>
-    <t>nicht ok</t>
-  </si>
-  <si>
-    <t>failed</t>
   </si>
   <si>
     <t>Es ist keine Änderungshistorie erkennbar.</t>
@@ -366,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -374,22 +359,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -397,7 +370,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -413,9 +386,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -453,7 +426,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -559,7 +532,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -701,7 +674,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -709,10 +682,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5654C6C7-1A31-4774-A3D9-6CA35CA298CC}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="72.42578125" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="38.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.42578125" customWidth="1"/>
+    <col min="3" max="3" width="99.7109375" customWidth="1"/>
+    <col min="4" max="4" width="43.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,423 +704,331 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" ht="115.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" ht="153.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" ht="115.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" ht="115.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="D12" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" ht="141" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="6" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="B15" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="C15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="D15" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="141" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="D16" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D17" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D18" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="102.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D19" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D20" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D21" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D22" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="115.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D23" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="102.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="77.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
+      <c r="D24" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="33" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>